--- a/files/九龙-何文田-128 Waterloo.xlsx
+++ b/files/九龙-何文田-128 Waterloo.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="128 Waterloo 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -708,7 +569,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-13</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -854,7 +715,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -950,7 +811,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -996,7 +857,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1042,7 +903,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1180,7 +1041,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1276,7 +1137,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1322,7 +1183,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1368,7 +1229,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1514,7 +1375,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1610,7 +1471,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1656,7 +1517,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1702,7 +1563,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1748,7 +1609,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1794,7 +1655,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1840,7 +1701,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1886,7 +1747,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1932,7 +1793,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1978,7 +1839,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2024,7 +1885,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-04</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2120,7 +1981,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2166,7 +2027,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2212,7 +2073,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-22</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2258,7 +2119,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2304,7 +2165,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2350,7 +2211,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2396,7 +2257,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-27</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2442,7 +2303,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2488,7 +2349,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2634,7 +2495,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2680,7 +2541,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2726,7 +2587,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2772,7 +2633,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2818,7 +2679,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2864,7 +2725,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-03-31</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2910,7 +2771,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-18</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2956,7 +2817,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-23</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3048,7 +2909,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-16</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3140,7 +3001,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-07</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3186,7 +3047,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-06</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3232,7 +3093,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-04-18</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3278,7 +3139,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-12-21</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3324,7 +3185,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3370,7 +3231,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-05</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3416,7 +3277,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-07-17</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3462,7 +3323,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-05</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3508,7 +3369,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3554,7 +3415,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-20</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3600,7 +3461,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-15</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3646,7 +3507,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-03-20</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3692,7 +3553,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-06-12</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3738,7 +3599,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3784,7 +3645,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3830,7 +3691,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-02-21</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3876,7 +3737,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-07</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3922,7 +3783,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3968,7 +3829,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-10</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -4014,7 +3875,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4060,7 +3921,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-27</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4106,7 +3967,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4152,7 +4013,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-03-31</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4198,7 +4059,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-11-07</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4244,7 +4105,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-04-27</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4290,7 +4151,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-10</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4336,7 +4197,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-01-09</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4382,7 +4243,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-12-30</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4428,7 +4289,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4474,7 +4335,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-04</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4520,7 +4381,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-03-14</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4566,7 +4427,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4612,7 +4473,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-05</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4658,7 +4519,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4704,7 +4565,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4750,7 +4611,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-02</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4796,7 +4657,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-13</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4842,7 +4703,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-05-24</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4888,7 +4749,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-01-30</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -4934,7 +4795,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-03</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -4980,7 +4841,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-03</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5026,7 +4887,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5072,7 +4933,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-07</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5118,7 +4979,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-02-19</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5164,7 +5025,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5210,7 +5071,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-08-26</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5256,7 +5117,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5302,7 +5163,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-03</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5348,7 +5209,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-04-21</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5394,7 +5255,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-04-08</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5440,7 +5301,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5486,7 +5347,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5532,7 +5393,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-07-05</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5578,7 +5439,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-03-31</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5624,7 +5485,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5670,7 +5531,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5716,7 +5577,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2021-04-25</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5762,7 +5623,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5784,1161 +5645,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:I21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>128 Waterloo - 128 Waterloo 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>110 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>98 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 3361呎 (4+房)
-$24,115万
-$71,749/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-      <c r="H6" s="17" t="inlineStr"/>
-      <c r="I6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 578呎 (2房)
-$2,563万
-$44,336/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 522呎 (2房)
-$1,892万
-$36,253/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 342呎 (1房)
-$1,307万
-$38,219/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>D | 842呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr"/>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 551呎 (2房)
-$1,480万
-$26,860/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H7" s="19" t="inlineStr">
-        <is>
-          <t>G | 535呎 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>H | 1257呎 (null房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 578呎 (2房)
-$1,954万
-$33,810/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 522呎 (2房)
-$2,122万
-$40,653/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 342呎 (1房)
-$1,281万
-$37,468/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 842呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr"/>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 551呎 (2房)
-$1,480万
-$26,860/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 535呎 (null房)
-$6,951万
-$129,927/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 1257呎 (null房)
-$6,951万
-$55,299/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 578呎 (2房)
-$2,372万
-$41,029/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 522呎 (2房)
-$2,060万
-$39,469/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 342呎 (1房)
-$1,256万
-$36,731/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 842呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr"/>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 551呎 (2房)
-$1,480万
-$26,860/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H9" s="19" t="inlineStr">
-        <is>
-          <t>G | 534呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
-        <is>
-          <t>H | 1258呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 578呎 (2房)
-$2,302万
-$39,834/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 522呎 (2房)
-$2,037万
-$39,027/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 342呎 (1房)
-$1,232万
-$36,009/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 842呎 (3房)
-$3,482万
-$41,355/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr"/>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 551呎 (2房)
-$2,490万
-$45,181/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 535呎 (2房)
-$2,413万
-$45,095/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 1257呎 (4+房)
-$4,570万
-$36,352/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 578呎 (2房)
-$2,220万
-$38,408/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 522呎 (2房)
-$1,978万
-$37,889/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 342呎 (1房)
-$1,207万
-$35,301/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 842呎 (3房)
-$3,073万
-$36,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr"/>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 551呎 (2房)
-$2,441万
-$44,294/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 535呎 (2房)
-$2,365万
-$44,209/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
-        <is>
-          <t>H | 1257呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 578呎 (2房)
-$1,970万
-$34,087/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 522呎 (2房)
-$1,920万
-$36,785/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>C | 342呎 (1房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 842呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr"/>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 551呎 (2房)
-$2,349万
-$42,635/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>G | 535呎 (2房)
-$2,277万
-$42,553/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>H | 1257呎 (4+房)
-$3,475万
-$27,645/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>A | 579呎 (2房)
-$1,951万
-$33,693/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 522呎 (2房)
-$1,440万
-$27,596/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 342呎 (1房)
-$1,064万
-$31,102/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 842呎 (3房)
-$2,922万
-$34,700/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr"/>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 551呎 (2房)
-$2,303万
-$41,797/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>G | 535呎 (2房)
-$1,900万
-$35,514/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>H | 1257呎 (4+房)
-$3,507万
-$27,901/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 578呎 (2房)
-$1,634万
-$28,265/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 522呎 (2房)
-$1,561万
-$29,910/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 342呎 (1房)
-$1,014万
-$29,661/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 842呎 (3房)
-$2,854万
-$33,900/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr"/>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 551呎 (2房)
-$1,777万
-$32,249/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H14" s="20" t="inlineStr">
-        <is>
-          <t>G | 534呎 (2房)
-$2,026万
-$37,940/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>H | 1257呎 (4+房)
-$3,368万
-$26,796/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 578呎 (2房)
-$1,714万
-$29,649/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 522呎 (2房)
-$1,538万
-$29,467/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 342呎 (1房)
-$1,000万
-$29,225/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 842呎 (3房)
-$2,745万
-$32,600/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr"/>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 551呎 (2房)
-$1,742万
-$31,617/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>G | 535呎 (2房)
-$1,817万
-$33,970/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>H | 1257呎 (4+房)
-$3,360万
-$26,730/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 579呎 (2房)
-$1,688万
-$29,161/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 522呎 (2房)
-$1,467万
-$28,098/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 342呎 (1房)
-$985万
-$28,789/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 842呎 (3房)
-$2,829万
-$33,600/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr"/>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 551呎 (2房)
-$1,898万
-$34,437/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>G | 535呎 (2房)
-$1,821万
-$34,032/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>H | 1257呎 (4+房)
-$3,300万
-$26,253/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 579呎 (2房)
-$1,562万
-$26,983/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 522呎 (2房)
-$1,357万
-$26,002/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 342呎 (1房)
-$985万
-$28,789/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 842呎 (3房)
-$2,745万
-$32,601/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr"/>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 551呎 (2房)
-$1,674万
-$30,388/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>G | 535呎 (2房)
-$1,623万
-$30,333/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>H | 1257呎 (4+房)
-$3,500万
-$27,844/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 578呎 (2房)
-$1,532万
-$26,500/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 522呎 (2房)
-$1,331万
-$25,490/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 342呎 (1房)
-$983万
-$28,731/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 527呎 (2房)
-$1,612万
-$30,584/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 332呎 (1房)
-$995万
-$29,961/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 552呎 (2房)
-$1,792万
-$32,455/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>G | 535呎 (2房)
-$1,733万
-$32,393/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>H | 1257呎 (4+房)
-$3,050万
-$24,264/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 579呎 (2房)
-$1,604万
-$27,698/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 522呎 (2房)
-$1,273万
-$24,393/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 342呎 (1房)
-$895万
-$26,170/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 527呎 (2房)
-$1,599万
-$30,340/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 332呎 (1房)
-$966万
-$29,087/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 552呎 (2房)
-$1,684万
-$30,498/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>G | 535呎 (2房)
-$1,602万
-$29,936/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>H | 1257呎 (4+房)
-$3,400万
-$27,049/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 578呎 (2房)
-$1,403万
-$24,266/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 522呎 (2房)
-$1,218万
-$23,343/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 342呎 (1房)
-$856万
-$25,044/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 527呎 (2房)
-$1,454万
-$27,583/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 332呎 (1房)
-$1,028万
-$30,970/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 552呎 (2房)
-$1,581万
-$28,645/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>G | 535呎 (2房)
-$1,661万
-$31,049/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>H | 1257呎 (4+房)
-$2,950万
-$23,469/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 556呎 (2房)
-$1,268万
-$22,806/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 521呎 (2房)
-$1,164万
-$22,338/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 342呎 (1房)
-$783万
-$22,889/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 527呎 (2房)
-$1,503万
-$28,514/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 331呎 (1房)
-$910万
-$27,502/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 552呎 (2房)
-$1,587万
-$28,746/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>G | 534呎 (2房)
-$1,442万
-$27,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>H | 1257呎 (4+房)
-$3,300万
-$26,253/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-何文田-128 Waterloo.xlsx
+++ b/files/九龙-何文田-128 Waterloo.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="128 Waterloo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,102 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +148,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +229,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +662,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -5645,4 +5833,1161 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>128 Waterloo 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 3361呎 (4+房)
+$24115万
+$71,749/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+      <c r="I5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 578呎 (2房)
+$2563万
+$44,336/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 522呎 (2房)
+$1892万
+$36,253/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$1307万
+$38,219/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>D | 842呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 551呎 (2房)
+$1480万
+$26,860/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>G | 535呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>H | 1257呎 (null房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 578呎 (2房)
+$1954万
+$33,810/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 522呎 (2房)
+$2122万
+$40,653/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$1281万
+$37,468/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 842呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 551呎 (2房)
+$1480万
+$26,860/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 535呎 (null房)
+$6951万
+$129,927/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 1257呎 (null房)
+$6951万
+$55,299/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 578呎 (2房)
+$2372万
+$41,029/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 522呎 (2房)
+$2060万
+$39,469/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$1256万
+$36,731/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 842呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr"/>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 551呎 (2房)
+$1480万
+$26,860/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>G | 534呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>H | 1258呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 578呎 (2房)
+$2302万
+$39,834/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 522呎 (2房)
+$2037万
+$39,027/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$1232万
+$36,009/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 842呎 (3房)
+$3482万
+$41,355/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 551呎 (2房)
+$2490万
+$45,181/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 535呎 (2房)
+$2413万
+$45,095/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 1257呎 (4+房)
+$4570万
+$36,352/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 578呎 (2房)
+$2220万
+$38,408/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 522呎 (2房)
+$1978万
+$37,889/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$1207万
+$35,301/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 842呎 (3房)
+$3073万
+$36,500/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 551呎 (2房)
+$2441万
+$44,294/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 535呎 (2房)
+$2365万
+$44,209/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>H | 1257呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 578呎 (2房)
+$1970万
+$34,087/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 522呎 (2房)
+$1920万
+$36,785/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 842呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr"/>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 551呎 (2房)
+$2349万
+$42,635/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 535呎 (2房)
+$2277万
+$42,553/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>H | 1257呎 (4+房)
+$3475万
+$27,645/呎
+(23年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>A | 579呎 (2房)
+$1951万
+$33,693/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 522呎 (2房)
+$1440万
+$27,596/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$1064万
+$31,102/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 842呎 (3房)
+$2922万
+$34,700/呎
+(22年-03月)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 551呎 (2房)
+$2303万
+$41,797/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 535呎 (2房)
+$1900万
+$35,514/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>H | 1257呎 (4+房)
+$3507万
+$27,901/呎
+(23年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 578呎 (2房)
+$1634万
+$28,265/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 522呎 (2房)
+$1561万
+$29,910/呎
+(22年-12月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$1014万
+$29,661/呎
+(23年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 842呎 (3房)
+$2854万
+$33,900/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 551呎 (2房)
+$1777万
+$32,249/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>G | 534呎 (2房)
+$2026万
+$37,940/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>H | 1257呎 (4+房)
+$3368万
+$26,796/呎
+(23年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 578呎 (2房)
+$1714万
+$29,649/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 522呎 (2房)
+$1538万
+$29,467/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$1000万
+$29,225/呎
+(23年-03月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 842呎 (3房)
+$2745万
+$32,600/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr"/>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 551呎 (2房)
+$1742万
+$31,617/呎
+(23年-06月)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 535呎 (2房)
+$1817万
+$33,970/呎
+(23年-07月)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>H | 1257呎 (4+房)
+$3360万
+$26,730/呎
+(23年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 579呎 (2房)
+$1688万
+$29,161/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 522呎 (2房)
+$1467万
+$28,098/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$985万
+$28,789/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 842呎 (3房)
+$2829万
+$33,600/呎
+(22年-02月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr"/>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 551呎 (2房)
+$1898万
+$34,437/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 535呎 (2房)
+$1821万
+$34,032/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>H | 1257呎 (4+房)
+$3300万
+$26,253/呎
+(23年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 579呎 (2房)
+$1562万
+$26,983/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 522呎 (2房)
+$1357万
+$26,002/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$985万
+$28,789/呎
+(22年-11月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 842呎 (3房)
+$2745万
+$32,601/呎
+(22年-03月)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 551呎 (2房)
+$1674万
+$30,388/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 535呎 (2房)
+$1623万
+$30,333/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 1257呎 (4+房)
+$3500万
+$27,844/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 578呎 (2房)
+$1532万
+$26,500/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 522呎 (2房)
+$1331万
+$25,490/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$983万
+$28,731/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 527呎 (2房)
+$1612万
+$30,584/呎
+(22年-03月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 332呎 (1房)
+$995万
+$29,961/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 552呎 (2房)
+$1792万
+$32,455/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 535呎 (2房)
+$1733万
+$32,393/呎
+(21年-12月)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>H | 1257呎 (4+房)
+$3050万
+$24,264/呎
+(23年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 579呎 (2房)
+$1604万
+$27,698/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 522呎 (2房)
+$1273万
+$24,393/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$895万
+$26,170/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 527呎 (2房)
+$1599万
+$30,340/呎
+(22年-01月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 332呎 (1房)
+$966万
+$29,087/呎
+(21年-05月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 552呎 (2房)
+$1684万
+$30,498/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 535呎 (2房)
+$1602万
+$29,936/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>H | 1257呎 (4+房)
+$3400万
+$27,049/呎
+(22年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 578呎 (2房)
+$1403万
+$24,266/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 522呎 (2房)
+$1218万
+$23,343/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$856万
+$25,044/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 527呎 (2房)
+$1454万
+$27,583/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 332呎 (1房)
+$1028万
+$30,970/呎
+(21年-08月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 552呎 (2房)
+$1581万
+$28,645/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 535呎 (2房)
+$1661万
+$31,049/呎
+(23年-02月)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>H | 1257呎 (4+房)
+$2950万
+$23,469/呎
+(23年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 556呎 (2房)
+$1268万
+$22,806/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 521呎 (2房)
+$1164万
+$22,338/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 342呎 (1房)
+$783万
+$22,889/呎
+(20年-11月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 527呎 (2房)
+$1503万
+$28,514/呎
+(22年-07月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 331呎 (1房)
+$910万
+$27,502/呎
+(21年-03月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 552呎 (2房)
+$1587万
+$28,746/呎
+(21年-07月)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 534呎 (2房)
+$1442万
+$27,000/呎
+(21年-04月)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 1257呎 (4+房)
+$3300万
+$26,253/呎
+(22年-10月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-何文田-128 Waterloo.xlsx
+++ b/files/九龙-何文田-128 Waterloo.xlsx
@@ -662,7 +662,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-何文田-128 Waterloo.xlsx
+++ b/files/九龙-何文田-128 Waterloo.xlsx
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J112"/>
+  <dimension ref="A1:N112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -665,6 +665,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -722,6 +726,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -768,6 +792,22 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>241150000</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>71749</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -818,6 +858,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -868,6 +928,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -914,6 +994,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>14800000</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>26860</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -964,6 +1060,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1010,6 +1126,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>13071000</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>38219</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1056,6 +1188,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>18924000</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>36253</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1102,6 +1250,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>25626000</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>44336</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1148,6 +1312,22 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>69511000</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>55299</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1194,6 +1374,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>69511000</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>129927</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1240,6 +1436,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>14800000</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>26860</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1290,6 +1502,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1336,6 +1568,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>12814000</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>37468</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1382,6 +1630,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>21221000</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>40653</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1428,6 +1692,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>19542000</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>33810</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1478,6 +1758,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1528,6 +1828,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1574,6 +1894,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>14800000</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>26860</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1624,6 +1960,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1670,6 +2026,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>12562000</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>36731</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1716,6 +2088,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>20603000</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>39469</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1762,6 +2150,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>23715000</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>41029</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1808,6 +2212,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>45695000</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>36352</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1854,6 +2274,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>24126000</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>45095</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1900,6 +2336,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>24895000</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>45181</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1946,6 +2398,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>34821000</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>41355</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1992,6 +2460,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>12315000</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>36009</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2038,6 +2522,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>20372000</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>39027</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2084,6 +2584,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>23024000</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>39834</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2134,6 +2650,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2180,6 +2716,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>23652000</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>44209</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2226,6 +2778,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>24406000</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>44294</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2272,6 +2840,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>30733000</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>36500</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2318,6 +2902,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>12073000</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>35301</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2364,6 +2964,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>19778000</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>37889</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2410,6 +3026,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>22200000</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>38408</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2456,6 +3088,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>34750000</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>27645</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2502,6 +3150,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>22766000</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>42553</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2548,6 +3212,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>23492000</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>42635</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2598,6 +3278,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2648,6 +3348,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2694,6 +3414,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>19202000</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>36785</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2740,6 +3476,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>19702000</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>34087</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2786,6 +3538,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>35071000</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>27901</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2832,6 +3600,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>19000000</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>35514</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2878,6 +3662,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>23030000</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>41797</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2924,6 +3724,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>29217400</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>34700</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2970,6 +3786,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>10637000</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>31102</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3016,6 +3848,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>14405000</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>27596</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3062,6 +3910,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>16581800</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>28639</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3108,6 +3972,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>33683000</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>26796</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3154,6 +4034,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>17221000</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>32249</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>120 天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3200,6 +4096,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>17769000</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>32249</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3246,6 +4158,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>28544000</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>33900</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3292,6 +4220,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>10144000</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>29661</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3338,6 +4282,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>15613000</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>29910</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3384,6 +4344,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>16337000</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>28265</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3430,6 +4406,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>33600000</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>26730</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3476,6 +4468,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>18174000</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>33970</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3522,6 +4530,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>17421000</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>31617</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3568,6 +4592,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>27449200</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>32600</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3614,6 +4654,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>9995000</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>29225</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3660,6 +4716,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>15382000</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>29467</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3706,6 +4778,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>17137000</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>29649</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3752,6 +4840,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>26253</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3798,6 +4902,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>18207000</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>34032</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3844,6 +4964,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>18975000</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>34437</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3890,6 +5026,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>28291000</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>33600</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3936,6 +5088,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>9846000</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>28789</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3982,6 +5150,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>14667000</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>28098</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4028,6 +5212,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>16884000</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>29161</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4074,6 +5274,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>27844</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4120,6 +5336,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>16228000</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>30333</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4166,6 +5398,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>16744000</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>30388</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4212,6 +5460,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>27450000</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>32601</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4258,6 +5522,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>9846000</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>28789</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4304,6 +5584,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>13573000</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>26002</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4350,6 +5646,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>15623000</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>26983</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4396,6 +5708,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>30500000</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>24264</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4442,6 +5770,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>17330000</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>32393</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4488,6 +5832,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>17915000</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>32455</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4534,6 +5894,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>9947000</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>29961</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4580,6 +5956,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>16118000</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>30584</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4626,6 +6018,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>9826000</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>28731</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4672,6 +6080,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>13306000</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>25490</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4718,6 +6142,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>15317000</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>26500</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4764,6 +6204,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>34000000</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>27049</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4810,6 +6266,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>16016000</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>29936</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4856,6 +6328,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>16835000</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>30498</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4902,6 +6390,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>9657000</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>29087</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4948,6 +6452,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>15989000</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>30340</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4994,6 +6514,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>8950000</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>26170</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5040,6 +6576,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>12733000</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>24393</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5086,6 +6638,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>16037000</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>27698</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5132,6 +6700,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>29500000</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>23469</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5178,6 +6762,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>16611000</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>31049</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5224,6 +6824,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>15812000</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>28645</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5270,6 +6886,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>10282000</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>30970</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5316,6 +6948,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>14536000</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>27583</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5362,6 +7010,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>8565000</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>25044</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5408,6 +7072,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>12185000</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>23343</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5454,6 +7134,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>14026000</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>24266</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5500,6 +7196,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>26253</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5546,6 +7258,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>14418000</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>27000</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5592,6 +7320,22 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>15868000</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>28746</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5638,6 +7382,22 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>9103000</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>27502</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5684,6 +7444,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>15027000</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>28514</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5730,6 +7506,22 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>7828000</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>22889</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5776,6 +7568,22 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>11638000</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>22338</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5822,13 +7630,29 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>12680000</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>22806</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -5984,7 +7808,7 @@
           <t>A | 3361呎 (4+房)
 $24115万
 $71,749/呎
-(22年-07月)</t>
+(22年-07月-13日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -6006,7 +7830,7 @@
           <t>A | 578呎 (2房)
 $2563万
 $44,336/呎
-(25年-04月)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -6014,7 +7838,7 @@
           <t>B | 522呎 (2房)
 $1892万
 $36,253/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -6022,7 +7846,7 @@
           <t>C | 342呎 (1房)
 $1307万
 $38,219/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -6039,7 +7863,7 @@
           <t>F | 551呎 (2房)
 $1480万
 $26,860/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -6070,7 +7894,7 @@
           <t>A | 578呎 (2房)
 $1954万
 $33,810/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -6078,7 +7902,7 @@
           <t>B | 522呎 (2房)
 $2122万
 $40,653/呎
-(25年-05月)</t>
+(25年-05月-12日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -6086,7 +7910,7 @@
           <t>C | 342呎 (1房)
 $1281万
 $37,468/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -6103,7 +7927,7 @@
           <t>F | 551呎 (2房)
 $1480万
 $26,860/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -6111,7 +7935,7 @@
           <t>G | 535呎 (null房)
 $6951万
 $129,927/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -6119,7 +7943,7 @@
           <t>H | 1257呎 (null房)
 $6951万
 $55,299/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -6134,7 +7958,7 @@
           <t>A | 578呎 (2房)
 $2372万
 $41,029/呎
-(25年-04月)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -6142,7 +7966,7 @@
           <t>B | 522呎 (2房)
 $2060万
 $39,469/呎
-(25年-05月)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -6150,7 +7974,7 @@
           <t>C | 342呎 (1房)
 $1256万
 $36,731/呎
-(25年-08月)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -6167,7 +7991,7 @@
           <t>F | 551呎 (2房)
 $1480万
 $26,860/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
@@ -6198,7 +8022,7 @@
           <t>A | 578呎 (2房)
 $2302万
 $39,834/呎
-(24年-09月)</t>
+(24年-09月-04日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -6206,7 +8030,7 @@
           <t>B | 522呎 (2房)
 $2037万
 $39,027/呎
-(24年-09月)</t>
+(24年-09月-04日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -6214,7 +8038,7 @@
           <t>C | 342呎 (1房)
 $1232万
 $36,009/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -6222,7 +8046,7 @@
           <t>D | 842呎 (3房)
 $3482万
 $41,355/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr"/>
@@ -6231,7 +8055,7 @@
           <t>F | 551呎 (2房)
 $2490万
 $45,181/呎
-(24年-07月)</t>
+(24年-07月-17日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -6239,7 +8063,7 @@
           <t>G | 535呎 (2房)
 $2413万
 $45,095/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -6247,7 +8071,7 @@
           <t>H | 1257呎 (4+房)
 $4570万
 $36,352/呎
-(25年-03月)</t>
+(25年-03月-10日)</t>
         </is>
       </c>
     </row>
@@ -6262,7 +8086,7 @@
           <t>A | 578呎 (2房)
 $2220万
 $38,408/呎
-(24年-06月)</t>
+(24年-06月-16日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -6270,7 +8094,7 @@
           <t>B | 522呎 (2房)
 $1978万
 $37,889/呎
-(24年-09月)</t>
+(24年-09月-18日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -6278,7 +8102,7 @@
           <t>C | 342呎 (1房)
 $1207万
 $35,301/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -6286,7 +8110,7 @@
           <t>D | 842呎 (3房)
 $3073万
 $36,500/呎
-(21年-12月)</t>
+(21年-12月-22日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr"/>
@@ -6295,7 +8119,7 @@
           <t>F | 551呎 (2房)
 $2441万
 $44,294/呎
-(24年-06月)</t>
+(24年-06月-24日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -6303,7 +8127,7 @@
           <t>G | 535呎 (2房)
 $2365万
 $44,209/呎
-(24年-06月)</t>
+(24年-06月-24日)</t>
         </is>
       </c>
       <c r="I10" s="24" t="inlineStr">
@@ -6326,7 +8150,7 @@
           <t>A | 578呎 (2房)
 $1970万
 $34,087/呎
-(24年-06月)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -6334,7 +8158,7 @@
           <t>B | 522呎 (2房)
 $1920万
 $36,785/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
@@ -6359,7 +8183,7 @@
           <t>F | 551呎 (2房)
 $2349万
 $42,635/呎
-(24年-07月)</t>
+(24年-07月-15日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -6367,7 +8191,7 @@
           <t>G | 535呎 (2房)
 $2277万
 $42,553/呎
-(24年-07月)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -6375,7 +8199,7 @@
           <t>H | 1257呎 (4+房)
 $3475万
 $27,645/呎
-(23年-02月)</t>
+(23年-02月-27日)</t>
         </is>
       </c>
     </row>
@@ -6398,7 +8222,7 @@
           <t>B | 522呎 (2房)
 $1440万
 $27,596/呎
-(23年-11月)</t>
+(23年-11月-23日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -6406,7 +8230,7 @@
           <t>C | 342呎 (1房)
 $1064万
 $31,102/呎
-(22年-01月)</t>
+(22年-01月-18日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -6414,7 +8238,7 @@
           <t>D | 842呎 (3房)
 $2922万
 $34,700/呎
-(22年-03月)</t>
+(22年-03月-31日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr"/>
@@ -6423,7 +8247,7 @@
           <t>F | 551呎 (2房)
 $2303万
 $41,797/呎
-(24年-07月)</t>
+(24年-07月-15日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -6431,7 +8255,7 @@
           <t>G | 535呎 (2房)
 $1900万
 $35,514/呎
-(23年-04月)</t>
+(23年-04月-17日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -6439,7 +8263,7 @@
           <t>H | 1257呎 (4+房)
 $3507万
 $27,901/呎
-(23年-02月)</t>
+(23年-02月-01日)</t>
         </is>
       </c>
     </row>
@@ -6454,7 +8278,7 @@
           <t>A | 578呎 (2房)
 $1634万
 $28,265/呎
-(23年-10月)</t>
+(23年-10月-10日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -6462,7 +8286,7 @@
           <t>B | 522呎 (2房)
 $1561万
 $29,910/呎
-(22年-12月)</t>
+(22年-12月-21日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -6470,7 +8294,7 @@
           <t>C | 342呎 (1房)
 $1014万
 $29,661/呎
-(23年-04月)</t>
+(23年-04月-18日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -6478,7 +8302,7 @@
           <t>D | 842呎 (3房)
 $2854万
 $33,900/呎
-(21年-05月)</t>
+(21年-05月-06日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr"/>
@@ -6487,7 +8311,7 @@
           <t>F | 551呎 (2房)
 $1777万
 $32,249/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="H13" s="24" t="inlineStr">
@@ -6503,7 +8327,7 @@
           <t>H | 1257呎 (4+房)
 $3368万
 $26,796/呎
-(23年-03月)</t>
+(23年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -6518,7 +8342,7 @@
           <t>A | 578呎 (2房)
 $1714万
 $29,649/呎
-(23年-03月)</t>
+(23年-03月-20日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -6526,7 +8350,7 @@
           <t>B | 522呎 (2房)
 $1538万
 $29,467/呎
-(21年-12月)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -6534,7 +8358,7 @@
           <t>C | 342呎 (1房)
 $1000万
 $29,225/呎
-(23年-03月)</t>
+(23年-03月-20日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -6542,7 +8366,7 @@
           <t>D | 842呎 (3房)
 $2745万
 $32,600/呎
-(21年-04月)</t>
+(21年-04月-27日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr"/>
@@ -6551,7 +8375,7 @@
           <t>F | 551呎 (2房)
 $1742万
 $31,617/呎
-(23年-06月)</t>
+(23年-06月-05日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -6559,7 +8383,7 @@
           <t>G | 535呎 (2房)
 $1817万
 $33,970/呎
-(23年-07月)</t>
+(23年-07月-17日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -6567,7 +8391,7 @@
           <t>H | 1257呎 (4+房)
 $3360万
 $26,730/呎
-(23年-02月)</t>
+(23年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -6582,7 +8406,7 @@
           <t>A | 579呎 (2房)
 $1688万
 $29,161/呎
-(21年-08月)</t>
+(21年-08月-10日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -6590,7 +8414,7 @@
           <t>B | 522呎 (2房)
 $1467万
 $28,098/呎
-(21年-12月)</t>
+(21年-12月-01日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -6598,7 +8422,7 @@
           <t>C | 342呎 (1房)
 $985万
 $28,789/呎
-(21年-12月)</t>
+(21年-12月-07日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -6606,7 +8430,7 @@
           <t>D | 842呎 (3房)
 $2829万
 $33,600/呎
-(22年-02月)</t>
+(22年-02月-21日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr"/>
@@ -6615,7 +8439,7 @@
           <t>F | 551呎 (2房)
 $1898万
 $34,437/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -6623,7 +8447,7 @@
           <t>G | 535呎 (2房)
 $1821万
 $34,032/呎
-(22年-01月)</t>
+(22年-01月-12日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -6631,7 +8455,7 @@
           <t>H | 1257呎 (4+房)
 $3300万
 $26,253/呎
-(23年-06月)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -6646,7 +8470,7 @@
           <t>A | 579呎 (2房)
 $1562万
 $26,983/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -6654,7 +8478,7 @@
           <t>B | 522呎 (2房)
 $1357万
 $26,002/呎
-(21年-04月)</t>
+(21年-04月-27日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -6662,7 +8486,7 @@
           <t>C | 342呎 (1房)
 $985万
 $28,789/呎
-(22年-11月)</t>
+(22年-11月-07日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -6670,7 +8494,7 @@
           <t>D | 842呎 (3房)
 $2745万
 $32,601/呎
-(22年-03月)</t>
+(22年-03月-31日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr"/>
@@ -6679,7 +8503,7 @@
           <t>F | 551呎 (2房)
 $1674万
 $30,388/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -6687,7 +8511,7 @@
           <t>G | 535呎 (2房)
 $1623万
 $30,333/呎
-(21年-05月)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -6695,7 +8519,7 @@
           <t>H | 1257呎 (4+房)
 $3500万
 $27,844/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
     </row>
@@ -6710,7 +8534,7 @@
           <t>A | 578呎 (2房)
 $1532万
 $26,500/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -6718,7 +8542,7 @@
           <t>B | 522呎 (2房)
 $1331万
 $25,490/呎
-(21年-05月)</t>
+(21年-05月-05日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -6726,7 +8550,7 @@
           <t>C | 342呎 (1房)
 $983万
 $28,731/呎
-(22年-01月)</t>
+(22年-01月-12日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -6734,7 +8558,7 @@
           <t>D | 527呎 (2房)
 $1612万
 $30,584/呎
-(22年-03月)</t>
+(22年-03月-14日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -6742,7 +8566,7 @@
           <t>E | 332呎 (1房)
 $995万
 $29,961/呎
-(20年-11月)</t>
+(20年-11月-04日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -6750,7 +8574,7 @@
           <t>F | 552呎 (2房)
 $1792万
 $32,455/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -6758,7 +8582,7 @@
           <t>G | 535呎 (2房)
 $1733万
 $32,393/呎
-(21年-12月)</t>
+(21年-12月-30日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -6766,7 +8590,7 @@
           <t>H | 1257呎 (4+房)
 $3050万
 $24,264/呎
-(23年-01月)</t>
+(23年-01月-09日)</t>
         </is>
       </c>
     </row>
@@ -6781,7 +8605,7 @@
           <t>A | 579呎 (2房)
 $1604万
 $27,698/呎
-(20年-11月)</t>
+(20年-11月-01日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -6789,7 +8613,7 @@
           <t>B | 522呎 (2房)
 $1273万
 $24,393/呎
-(20年-11月)</t>
+(20年-11月-03日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -6797,7 +8621,7 @@
           <t>C | 342呎 (1房)
 $895万
 $26,170/呎
-(20年-11月)</t>
+(20年-11月-03日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -6805,7 +8629,7 @@
           <t>D | 527呎 (2房)
 $1599万
 $30,340/呎
-(22年-01月)</t>
+(22年-01月-30日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -6813,7 +8637,7 @@
           <t>E | 332呎 (1房)
 $966万
 $29,087/呎
-(21年-05月)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -6821,7 +8645,7 @@
           <t>F | 552呎 (2房)
 $1684万
 $30,498/呎
-(21年-07月)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -6829,7 +8653,7 @@
           <t>G | 535呎 (2房)
 $1602万
 $29,936/呎
-(20年-11月)</t>
+(20年-11月-02日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -6837,7 +8661,7 @@
           <t>H | 1257呎 (4+房)
 $3400万
 $27,049/呎
-(22年-10月)</t>
+(22年-10月-31日)</t>
         </is>
       </c>
     </row>
@@ -6852,7 +8676,7 @@
           <t>A | 578呎 (2房)
 $1403万
 $24,266/呎
-(21年-04月)</t>
+(21年-04月-08日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -6860,7 +8684,7 @@
           <t>B | 522呎 (2房)
 $1218万
 $23,343/呎
-(21年-04月)</t>
+(21年-04月-21日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -6868,7 +8692,7 @@
           <t>C | 342呎 (1房)
 $856万
 $25,044/呎
-(20年-11月)</t>
+(20年-11月-03日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -6876,7 +8700,7 @@
           <t>D | 527呎 (2房)
 $1454万
 $27,583/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -6884,7 +8708,7 @@
           <t>E | 332呎 (1房)
 $1028万
 $30,970/呎
-(21年-08月)</t>
+(21年-08月-26日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -6892,7 +8716,7 @@
           <t>F | 552呎 (2房)
 $1581万
 $28,645/呎
-(23年-10月)</t>
+(23年-10月-24日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -6900,7 +8724,7 @@
           <t>G | 535呎 (2房)
 $1661万
 $31,049/呎
-(23年-02月)</t>
+(23年-02月-19日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -6908,7 +8732,7 @@
           <t>H | 1257呎 (4+房)
 $2950万
 $23,469/呎
-(23年-02月)</t>
+(23年-02月-07日)</t>
         </is>
       </c>
     </row>
@@ -6923,7 +8747,7 @@
           <t>A | 556呎 (2房)
 $1268万
 $22,806/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -6931,7 +8755,7 @@
           <t>B | 521呎 (2房)
 $1164万
 $22,338/呎
-(21年-04月)</t>
+(21年-04月-25日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -6939,7 +8763,7 @@
           <t>C | 342呎 (1房)
 $783万
 $22,889/呎
-(20年-11月)</t>
+(20年-11月-01日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -6947,7 +8771,7 @@
           <t>D | 527呎 (2房)
 $1503万
 $28,514/呎
-(22年-07月)</t>
+(22年-07月-06日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -6955,7 +8779,7 @@
           <t>E | 331呎 (1房)
 $910万
 $27,502/呎
-(21年-03月)</t>
+(21年-03月-31日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -6963,7 +8787,7 @@
           <t>F | 552呎 (2房)
 $1587万
 $28,746/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -6971,7 +8795,7 @@
           <t>G | 534呎 (2房)
 $1442万
 $27,000/呎
-(21年-04月)</t>
+(21年-04月-12日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -6979,7 +8803,7 @@
           <t>H | 1257呎 (4+房)
 $3300万
 $26,253/呎
-(22年-10月)</t>
+(22年-10月-31日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-128 Waterloo.xlsx
+++ b/files/九龙-何文田-128 Waterloo.xlsx
@@ -3894,7 +3894,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -3902,31 +3902,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H52" s="5" t="n">
-        <v>19508000</v>
-      </c>
-      <c r="I52" s="5" t="n">
-        <v>33693</v>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="n">
-        <v>16581800</v>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v>28639</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>120 天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7734,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -7741,7 +7749,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -8209,12 +8217,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 579呎 (2房)
-$1951万
-$33,693/呎
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">

--- a/files/九龙-何文田-128 Waterloo.xlsx
+++ b/files/九龙-何文田-128 Waterloo.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -136,6 +136,11 @@
       <color rgb="00000000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -213,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -285,6 +290,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3894,7 +3902,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -3902,39 +3910,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H52" s="5" t="n">
+        <v>19508000</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>33693</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K52" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L52" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>16581800</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>28639</v>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>120 天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7734,12 +7734,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -7816,7 +7816,7 @@
           <t>A | 3361呎 (4+房)
 $24115万
 $71,749/呎
-(22年-07月-13日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -7838,7 +7838,7 @@
           <t>A | 578呎 (2房)
 $2563万
 $44,336/呎
-(25年-04月-22日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -7846,7 +7846,7 @@
           <t>B | 522呎 (2房)
 $1892万
 $36,253/呎
-(25年-08月-11日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -7854,7 +7854,7 @@
           <t>C | 342呎 (1房)
 $1307万
 $38,219/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -7871,7 +7871,7 @@
           <t>F | 551呎 (2房)
 $1480万
 $26,860/呎
-(26年-06月-03日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -7902,7 +7902,7 @@
           <t>A | 578呎 (2房)
 $1954万
 $33,810/呎
-(25年-08月-11日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -7910,7 +7910,7 @@
           <t>B | 522呎 (2房)
 $2122万
 $40,653/呎
-(25年-05月-12日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -7918,7 +7918,7 @@
           <t>C | 342呎 (1房)
 $1281万
 $37,468/呎
-(25年-08月-26日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -7935,7 +7935,7 @@
           <t>F | 551呎 (2房)
 $1480万
 $26,860/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -7943,7 +7943,7 @@
           <t>G | 535呎 (null房)
 $6951万
 $129,927/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -7951,7 +7951,7 @@
           <t>H | 1257呎 (null房)
 $6951万
 $55,299/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -7966,7 +7966,7 @@
           <t>A | 578呎 (2房)
 $2372万
 $41,029/呎
-(25年-04月-28日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -7974,7 +7974,7 @@
           <t>B | 522呎 (2房)
 $2060万
 $39,469/呎
-(25年-05月-08日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -7982,7 +7982,7 @@
           <t>C | 342呎 (1房)
 $1256万
 $36,731/呎
-(25年-08月-25日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -7999,7 +7999,7 @@
           <t>F | 551呎 (2房)
 $1480万
 $26,860/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
@@ -8030,7 +8030,7 @@
           <t>A | 578呎 (2房)
 $2302万
 $39,834/呎
-(24年-09月-04日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -8038,7 +8038,7 @@
           <t>B | 522呎 (2房)
 $2037万
 $39,027/呎
-(24年-09月-04日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -8046,7 +8046,7 @@
           <t>C | 342呎 (1房)
 $1232万
 $36,009/呎
-(25年-03月-18日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -8054,7 +8054,7 @@
           <t>D | 842呎 (3房)
 $3482万
 $41,355/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr"/>
@@ -8063,7 +8063,7 @@
           <t>F | 551呎 (2房)
 $2490万
 $45,181/呎
-(24年-07月-17日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -8071,7 +8071,7 @@
           <t>G | 535呎 (2房)
 $2413万
 $45,095/呎
-(24年-07月-31日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -8079,7 +8079,7 @@
           <t>H | 1257呎 (4+房)
 $4570万
 $36,352/呎
-(25年-03月-10日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -8094,7 +8094,7 @@
           <t>A | 578呎 (2房)
 $2220万
 $38,408/呎
-(24年-06月-16日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -8102,7 +8102,7 @@
           <t>B | 522呎 (2房)
 $1978万
 $37,889/呎
-(24年-09月-18日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -8110,7 +8110,7 @@
           <t>C | 342呎 (1房)
 $1207万
 $35,301/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -8118,7 +8118,7 @@
           <t>D | 842呎 (3房)
 $3073万
 $36,500/呎
-(21年-12月-22日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr"/>
@@ -8127,7 +8127,7 @@
           <t>F | 551呎 (2房)
 $2441万
 $44,294/呎
-(24年-06月-24日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -8135,7 +8135,7 @@
           <t>G | 535呎 (2房)
 $2365万
 $44,209/呎
-(24年-06月-24日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="I10" s="24" t="inlineStr">
@@ -8158,7 +8158,7 @@
           <t>A | 578呎 (2房)
 $1970万
 $34,087/呎
-(24年-06月-04日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -8166,7 +8166,7 @@
           <t>B | 522呎 (2房)
 $1920万
 $36,785/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
@@ -8191,7 +8191,7 @@
           <t>F | 551呎 (2房)
 $2349万
 $42,635/呎
-(24年-07月-15日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -8199,7 +8199,7 @@
           <t>G | 535呎 (2房)
 $2277万
 $42,553/呎
-(24年-07月-03日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -8207,7 +8207,7 @@
           <t>H | 1257呎 (4+房)
 $3475万
 $27,645/呎
-(23年-02月-27日)</t>
+(23年-02月)</t>
         </is>
       </c>
     </row>
@@ -8217,12 +8217,12 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>A | 579呎 (2房)
-招标单位
--
-(在售)</t>
+$1951万
+$33,693/呎
+(已定价未售)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -8230,7 +8230,7 @@
           <t>B | 522呎 (2房)
 $1440万
 $27,596/呎
-(23年-11月-23日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -8238,7 +8238,7 @@
           <t>C | 342呎 (1房)
 $1064万
 $31,102/呎
-(22年-01月-18日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -8246,7 +8246,7 @@
           <t>D | 842呎 (3房)
 $2922万
 $34,700/呎
-(22年-03月-31日)</t>
+(22年-03月)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr"/>
@@ -8255,7 +8255,7 @@
           <t>F | 551呎 (2房)
 $2303万
 $41,797/呎
-(24年-07月-15日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -8263,7 +8263,7 @@
           <t>G | 535呎 (2房)
 $1900万
 $35,514/呎
-(23年-04月-17日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -8271,7 +8271,7 @@
           <t>H | 1257呎 (4+房)
 $3507万
 $27,901/呎
-(23年-02月-01日)</t>
+(23年-02月)</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
           <t>A | 578呎 (2房)
 $1634万
 $28,265/呎
-(23年-10月-10日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -8294,7 +8294,7 @@
           <t>B | 522呎 (2房)
 $1561万
 $29,910/呎
-(22年-12月-21日)</t>
+(22年-12月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -8302,7 +8302,7 @@
           <t>C | 342呎 (1房)
 $1014万
 $29,661/呎
-(23年-04月-18日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -8310,7 +8310,7 @@
           <t>D | 842呎 (3房)
 $2854万
 $33,900/呎
-(21年-05月-06日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr"/>
@@ -8319,7 +8319,7 @@
           <t>F | 551呎 (2房)
 $1777万
 $32,249/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="H13" s="24" t="inlineStr">
@@ -8335,7 +8335,7 @@
           <t>H | 1257呎 (4+房)
 $3368万
 $26,796/呎
-(23年-03月-16日)</t>
+(23年-03月)</t>
         </is>
       </c>
     </row>
@@ -8350,7 +8350,7 @@
           <t>A | 578呎 (2房)
 $1714万
 $29,649/呎
-(23年-03月-20日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -8358,7 +8358,7 @@
           <t>B | 522呎 (2房)
 $1538万
 $29,467/呎
-(21年-12月-15日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -8366,7 +8366,7 @@
           <t>C | 342呎 (1房)
 $1000万
 $29,225/呎
-(23年-03月-20日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -8374,7 +8374,7 @@
           <t>D | 842呎 (3房)
 $2745万
 $32,600/呎
-(21年-04月-27日)</t>
+(21年-04月)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr"/>
@@ -8383,7 +8383,7 @@
           <t>F | 551呎 (2房)
 $1742万
 $31,617/呎
-(23年-06月-05日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -8391,7 +8391,7 @@
           <t>G | 535呎 (2房)
 $1817万
 $33,970/呎
-(23年-07月-17日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -8399,7 +8399,7 @@
           <t>H | 1257呎 (4+房)
 $3360万
 $26,730/呎
-(23年-02月-05日)</t>
+(23年-02月)</t>
         </is>
       </c>
     </row>
@@ -8414,7 +8414,7 @@
           <t>A | 579呎 (2房)
 $1688万
 $29,161/呎
-(21年-08月-10日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -8422,7 +8422,7 @@
           <t>B | 522呎 (2房)
 $1467万
 $28,098/呎
-(21年-12月-01日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -8430,7 +8430,7 @@
           <t>C | 342呎 (1房)
 $985万
 $28,789/呎
-(21年-12月-07日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -8438,7 +8438,7 @@
           <t>D | 842呎 (3房)
 $2829万
 $33,600/呎
-(22年-02月-21日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr"/>
@@ -8447,7 +8447,7 @@
           <t>F | 551呎 (2房)
 $1898万
 $34,437/呎
-(25年-08月-24日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -8455,7 +8455,7 @@
           <t>G | 535呎 (2房)
 $1821万
 $34,032/呎
-(22年-01月-12日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -8463,7 +8463,7 @@
           <t>H | 1257呎 (4+房)
 $3300万
 $26,253/呎
-(23年-06月-12日)</t>
+(23年-06月)</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
           <t>A | 579呎 (2房)
 $1562万
 $26,983/呎
-(24年-04月-10日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -8486,7 +8486,7 @@
           <t>B | 522呎 (2房)
 $1357万
 $26,002/呎
-(21年-04月-27日)</t>
+(21年-04月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8494,7 +8494,7 @@
           <t>C | 342呎 (1房)
 $985万
 $28,789/呎
-(22年-11月-07日)</t>
+(22年-11月)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -8502,7 +8502,7 @@
           <t>D | 842呎 (3房)
 $2745万
 $32,601/呎
-(22年-03月-31日)</t>
+(22年-03月)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr"/>
@@ -8511,7 +8511,7 @@
           <t>F | 551呎 (2房)
 $1674万
 $30,388/呎
-(24年-03月-24日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -8519,7 +8519,7 @@
           <t>G | 535呎 (2房)
 $1623万
 $30,333/呎
-(21年-05月-27日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -8527,7 +8527,7 @@
           <t>H | 1257呎 (4+房)
 $3500万
 $27,844/呎
-(25年-11月-19日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
           <t>A | 578呎 (2房)
 $1532万
 $26,500/呎
-(24年-05月-01日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -8550,7 +8550,7 @@
           <t>B | 522呎 (2房)
 $1331万
 $25,490/呎
-(21年-05月-05日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -8558,7 +8558,7 @@
           <t>C | 342呎 (1房)
 $983万
 $28,731/呎
-(22年-01月-12日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -8566,7 +8566,7 @@
           <t>D | 527呎 (2房)
 $1612万
 $30,584/呎
-(22年-03月-14日)</t>
+(22年-03月)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -8574,7 +8574,7 @@
           <t>E | 332呎 (1房)
 $995万
 $29,961/呎
-(20年-11月-04日)</t>
+(20年-11月)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -8582,7 +8582,7 @@
           <t>F | 552呎 (2房)
 $1792万
 $32,455/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -8590,7 +8590,7 @@
           <t>G | 535呎 (2房)
 $1733万
 $32,393/呎
-(21年-12月-30日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -8598,7 +8598,7 @@
           <t>H | 1257呎 (4+房)
 $3050万
 $24,264/呎
-(23年-01月-09日)</t>
+(23年-01月)</t>
         </is>
       </c>
     </row>
@@ -8613,7 +8613,7 @@
           <t>A | 579呎 (2房)
 $1604万
 $27,698/呎
-(20年-11月-01日)</t>
+(20年-11月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -8621,7 +8621,7 @@
           <t>B | 522呎 (2房)
 $1273万
 $24,393/呎
-(20年-11月-03日)</t>
+(20年-11月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -8629,7 +8629,7 @@
           <t>C | 342呎 (1房)
 $895万
 $26,170/呎
-(20年-11月-03日)</t>
+(20年-11月)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -8637,7 +8637,7 @@
           <t>D | 527呎 (2房)
 $1599万
 $30,340/呎
-(22年-01月-30日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -8645,7 +8645,7 @@
           <t>E | 332呎 (1房)
 $966万
 $29,087/呎
-(21年-05月-24日)</t>
+(21年-05月)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -8653,7 +8653,7 @@
           <t>F | 552呎 (2房)
 $1684万
 $30,498/呎
-(21年-07月-13日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -8661,7 +8661,7 @@
           <t>G | 535呎 (2房)
 $1602万
 $29,936/呎
-(20年-11月-02日)</t>
+(20年-11月)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -8669,7 +8669,7 @@
           <t>H | 1257呎 (4+房)
 $3400万
 $27,049/呎
-(22年-10月-31日)</t>
+(22年-10月)</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8684,7 @@
           <t>A | 578呎 (2房)
 $1403万
 $24,266/呎
-(21年-04月-08日)</t>
+(21年-04月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -8692,7 +8692,7 @@
           <t>B | 522呎 (2房)
 $1218万
 $23,343/呎
-(21年-04月-21日)</t>
+(21年-04月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -8700,7 +8700,7 @@
           <t>C | 342呎 (1房)
 $856万
 $25,044/呎
-(20年-11月-03日)</t>
+(20年-11月)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -8708,7 +8708,7 @@
           <t>D | 527呎 (2房)
 $1454万
 $27,583/呎
-(24年-05月-01日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -8716,7 +8716,7 @@
           <t>E | 332呎 (1房)
 $1028万
 $30,970/呎
-(21年-08月-26日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -8724,7 +8724,7 @@
           <t>F | 552呎 (2房)
 $1581万
 $28,645/呎
-(23年-10月-24日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -8732,7 +8732,7 @@
           <t>G | 535呎 (2房)
 $1661万
 $31,049/呎
-(23年-02月-19日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -8740,7 +8740,7 @@
           <t>H | 1257呎 (4+房)
 $2950万
 $23,469/呎
-(23年-02月-07日)</t>
+(23年-02月)</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8755,7 @@
           <t>A | 556呎 (2房)
 $1268万
 $22,806/呎
-(26年-03月-23日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -8763,7 +8763,7 @@
           <t>B | 521呎 (2房)
 $1164万
 $22,338/呎
-(21年-04月-25日)</t>
+(21年-04月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -8771,7 +8771,7 @@
           <t>C | 342呎 (1房)
 $783万
 $22,889/呎
-(20年-11月-01日)</t>
+(20年-11月)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -8779,7 +8779,7 @@
           <t>D | 527呎 (2房)
 $1503万
 $28,514/呎
-(22年-07月-06日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -8787,7 +8787,7 @@
           <t>E | 331呎 (1房)
 $910万
 $27,502/呎
-(21年-03月-31日)</t>
+(21年-03月)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -8795,7 +8795,7 @@
           <t>F | 552呎 (2房)
 $1587万
 $28,746/呎
-(21年-07月-05日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -8803,7 +8803,7 @@
           <t>G | 534呎 (2房)
 $1442万
 $27,000/呎
-(21年-04月-12日)</t>
+(21年-04月)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -8811,7 +8811,7 @@
           <t>H | 1257呎 (4+房)
 $3300万
 $26,253/呎
-(22年-10月-31日)</t>
+(22年-10月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-128 Waterloo.xlsx
+++ b/files/九龙-何文田-128 Waterloo.xlsx
@@ -7816,7 +7816,7 @@
           <t>A | 3361呎 (4+房)
 $24115万
 $71,749/呎
-(22年-07月)</t>
+(22年-07月-13日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -7838,7 +7838,7 @@
           <t>A | 578呎 (2房)
 $2563万
 $44,336/呎
-(25年-04月)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -7846,7 +7846,7 @@
           <t>B | 522呎 (2房)
 $1892万
 $36,253/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -7854,7 +7854,7 @@
           <t>C | 342呎 (1房)
 $1307万
 $38,219/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -7871,7 +7871,7 @@
           <t>F | 551呎 (2房)
 $1480万
 $26,860/呎
-(26年-06月)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -7902,7 +7902,7 @@
           <t>A | 578呎 (2房)
 $1954万
 $33,810/呎
-(25年-08月)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -7910,7 +7910,7 @@
           <t>B | 522呎 (2房)
 $2122万
 $40,653/呎
-(25年-05月)</t>
+(25年-05月-12日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -7918,7 +7918,7 @@
           <t>C | 342呎 (1房)
 $1281万
 $37,468/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -7935,7 +7935,7 @@
           <t>F | 551呎 (2房)
 $1480万
 $26,860/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -7943,7 +7943,7 @@
           <t>G | 535呎 (null房)
 $6951万
 $129,927/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -7951,7 +7951,7 @@
           <t>H | 1257呎 (null房)
 $6951万
 $55,299/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -7966,7 +7966,7 @@
           <t>A | 578呎 (2房)
 $2372万
 $41,029/呎
-(25年-04月)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -7974,7 +7974,7 @@
           <t>B | 522呎 (2房)
 $2060万
 $39,469/呎
-(25年-05月)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -7982,7 +7982,7 @@
           <t>C | 342呎 (1房)
 $1256万
 $36,731/呎
-(25年-08月)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -7999,7 +7999,7 @@
           <t>F | 551呎 (2房)
 $1480万
 $26,860/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="H8" s="23" t="inlineStr">
@@ -8030,7 +8030,7 @@
           <t>A | 578呎 (2房)
 $2302万
 $39,834/呎
-(24年-09月)</t>
+(24年-09月-04日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -8038,7 +8038,7 @@
           <t>B | 522呎 (2房)
 $2037万
 $39,027/呎
-(24年-09月)</t>
+(24年-09月-04日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -8046,7 +8046,7 @@
           <t>C | 342呎 (1房)
 $1232万
 $36,009/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -8054,7 +8054,7 @@
           <t>D | 842呎 (3房)
 $3482万
 $41,355/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr"/>
@@ -8063,7 +8063,7 @@
           <t>F | 551呎 (2房)
 $2490万
 $45,181/呎
-(24年-07月)</t>
+(24年-07月-17日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -8071,7 +8071,7 @@
           <t>G | 535呎 (2房)
 $2413万
 $45,095/呎
-(24年-07月)</t>
+(24年-07月-31日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -8079,7 +8079,7 @@
           <t>H | 1257呎 (4+房)
 $4570万
 $36,352/呎
-(25年-03月)</t>
+(25年-03月-10日)</t>
         </is>
       </c>
     </row>
@@ -8094,7 +8094,7 @@
           <t>A | 578呎 (2房)
 $2220万
 $38,408/呎
-(24年-06月)</t>
+(24年-06月-16日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -8102,7 +8102,7 @@
           <t>B | 522呎 (2房)
 $1978万
 $37,889/呎
-(24年-09月)</t>
+(24年-09月-18日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -8110,7 +8110,7 @@
           <t>C | 342呎 (1房)
 $1207万
 $35,301/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -8118,7 +8118,7 @@
           <t>D | 842呎 (3房)
 $3073万
 $36,500/呎
-(21年-12月)</t>
+(21年-12月-22日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr"/>
@@ -8127,7 +8127,7 @@
           <t>F | 551呎 (2房)
 $2441万
 $44,294/呎
-(24年-06月)</t>
+(24年-06月-24日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -8135,7 +8135,7 @@
           <t>G | 535呎 (2房)
 $2365万
 $44,209/呎
-(24年-06月)</t>
+(24年-06月-24日)</t>
         </is>
       </c>
       <c r="I10" s="24" t="inlineStr">
@@ -8158,7 +8158,7 @@
           <t>A | 578呎 (2房)
 $1970万
 $34,087/呎
-(24年-06月)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -8166,7 +8166,7 @@
           <t>B | 522呎 (2房)
 $1920万
 $36,785/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
@@ -8191,7 +8191,7 @@
           <t>F | 551呎 (2房)
 $2349万
 $42,635/呎
-(24年-07月)</t>
+(24年-07月-15日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -8199,7 +8199,7 @@
           <t>G | 535呎 (2房)
 $2277万
 $42,553/呎
-(24年-07月)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -8207,7 +8207,7 @@
           <t>H | 1257呎 (4+房)
 $3475万
 $27,645/呎
-(23年-02月)</t>
+(23年-02月-27日)</t>
         </is>
       </c>
     </row>
@@ -8230,7 +8230,7 @@
           <t>B | 522呎 (2房)
 $1440万
 $27,596/呎
-(23年-11月)</t>
+(23年-11月-23日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -8238,7 +8238,7 @@
           <t>C | 342呎 (1房)
 $1064万
 $31,102/呎
-(22年-01月)</t>
+(22年-01月-18日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -8246,7 +8246,7 @@
           <t>D | 842呎 (3房)
 $2922万
 $34,700/呎
-(22年-03月)</t>
+(22年-03月-31日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr"/>
@@ -8255,7 +8255,7 @@
           <t>F | 551呎 (2房)
 $2303万
 $41,797/呎
-(24年-07月)</t>
+(24年-07月-15日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -8263,7 +8263,7 @@
           <t>G | 535呎 (2房)
 $1900万
 $35,514/呎
-(23年-04月)</t>
+(23年-04月-17日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -8271,7 +8271,7 @@
           <t>H | 1257呎 (4+房)
 $3507万
 $27,901/呎
-(23年-02月)</t>
+(23年-02月-01日)</t>
         </is>
       </c>
     </row>
@@ -8286,7 +8286,7 @@
           <t>A | 578呎 (2房)
 $1634万
 $28,265/呎
-(23年-10月)</t>
+(23年-10月-10日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -8294,7 +8294,7 @@
           <t>B | 522呎 (2房)
 $1561万
 $29,910/呎
-(22年-12月)</t>
+(22年-12月-21日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -8302,7 +8302,7 @@
           <t>C | 342呎 (1房)
 $1014万
 $29,661/呎
-(23年-04月)</t>
+(23年-04月-18日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -8310,7 +8310,7 @@
           <t>D | 842呎 (3房)
 $2854万
 $33,900/呎
-(21年-05月)</t>
+(21年-05月-06日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr"/>
@@ -8319,7 +8319,7 @@
           <t>F | 551呎 (2房)
 $1777万
 $32,249/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="H13" s="24" t="inlineStr">
@@ -8335,7 +8335,7 @@
           <t>H | 1257呎 (4+房)
 $3368万
 $26,796/呎
-(23年-03月)</t>
+(23年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -8350,7 +8350,7 @@
           <t>A | 578呎 (2房)
 $1714万
 $29,649/呎
-(23年-03月)</t>
+(23年-03月-20日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -8358,7 +8358,7 @@
           <t>B | 522呎 (2房)
 $1538万
 $29,467/呎
-(21年-12月)</t>
+(21年-12月-15日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -8366,7 +8366,7 @@
           <t>C | 342呎 (1房)
 $1000万
 $29,225/呎
-(23年-03月)</t>
+(23年-03月-20日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -8374,7 +8374,7 @@
           <t>D | 842呎 (3房)
 $2745万
 $32,600/呎
-(21年-04月)</t>
+(21年-04月-27日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr"/>
@@ -8383,7 +8383,7 @@
           <t>F | 551呎 (2房)
 $1742万
 $31,617/呎
-(23年-06月)</t>
+(23年-06月-05日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -8391,7 +8391,7 @@
           <t>G | 535呎 (2房)
 $1817万
 $33,970/呎
-(23年-07月)</t>
+(23年-07月-17日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -8399,7 +8399,7 @@
           <t>H | 1257呎 (4+房)
 $3360万
 $26,730/呎
-(23年-02月)</t>
+(23年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -8414,7 +8414,7 @@
           <t>A | 579呎 (2房)
 $1688万
 $29,161/呎
-(21年-08月)</t>
+(21年-08月-10日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -8422,7 +8422,7 @@
           <t>B | 522呎 (2房)
 $1467万
 $28,098/呎
-(21年-12月)</t>
+(21年-12月-01日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -8430,7 +8430,7 @@
           <t>C | 342呎 (1房)
 $985万
 $28,789/呎
-(21年-12月)</t>
+(21年-12月-07日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -8438,7 +8438,7 @@
           <t>D | 842呎 (3房)
 $2829万
 $33,600/呎
-(22年-02月)</t>
+(22年-02月-21日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr"/>
@@ -8447,7 +8447,7 @@
           <t>F | 551呎 (2房)
 $1898万
 $34,437/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -8455,7 +8455,7 @@
           <t>G | 535呎 (2房)
 $1821万
 $34,032/呎
-(22年-01月)</t>
+(22年-01月-12日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -8463,7 +8463,7 @@
           <t>H | 1257呎 (4+房)
 $3300万
 $26,253/呎
-(23年-06月)</t>
+(23年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
           <t>A | 579呎 (2房)
 $1562万
 $26,983/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -8486,7 +8486,7 @@
           <t>B | 522呎 (2房)
 $1357万
 $26,002/呎
-(21年-04月)</t>
+(21年-04月-27日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8494,7 +8494,7 @@
           <t>C | 342呎 (1房)
 $985万
 $28,789/呎
-(22年-11月)</t>
+(22年-11月-07日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -8502,7 +8502,7 @@
           <t>D | 842呎 (3房)
 $2745万
 $32,601/呎
-(22年-03月)</t>
+(22年-03月-31日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr"/>
@@ -8511,7 +8511,7 @@
           <t>F | 551呎 (2房)
 $1674万
 $30,388/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -8519,7 +8519,7 @@
           <t>G | 535呎 (2房)
 $1623万
 $30,333/呎
-(21年-05月)</t>
+(21年-05月-27日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -8527,7 +8527,7 @@
           <t>H | 1257呎 (4+房)
 $3500万
 $27,844/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
           <t>A | 578呎 (2房)
 $1532万
 $26,500/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -8550,7 +8550,7 @@
           <t>B | 522呎 (2房)
 $1331万
 $25,490/呎
-(21年-05月)</t>
+(21年-05月-05日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -8558,7 +8558,7 @@
           <t>C | 342呎 (1房)
 $983万
 $28,731/呎
-(22年-01月)</t>
+(22年-01月-12日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -8566,7 +8566,7 @@
           <t>D | 527呎 (2房)
 $1612万
 $30,584/呎
-(22年-03月)</t>
+(22年-03月-14日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -8574,7 +8574,7 @@
           <t>E | 332呎 (1房)
 $995万
 $29,961/呎
-(20年-11月)</t>
+(20年-11月-04日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -8582,7 +8582,7 @@
           <t>F | 552呎 (2房)
 $1792万
 $32,455/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -8590,7 +8590,7 @@
           <t>G | 535呎 (2房)
 $1733万
 $32,393/呎
-(21年-12月)</t>
+(21年-12月-30日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -8598,7 +8598,7 @@
           <t>H | 1257呎 (4+房)
 $3050万
 $24,264/呎
-(23年-01月)</t>
+(23年-01月-09日)</t>
         </is>
       </c>
     </row>
@@ -8613,7 +8613,7 @@
           <t>A | 579呎 (2房)
 $1604万
 $27,698/呎
-(20年-11月)</t>
+(20年-11月-01日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -8621,7 +8621,7 @@
           <t>B | 522呎 (2房)
 $1273万
 $24,393/呎
-(20年-11月)</t>
+(20年-11月-03日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -8629,7 +8629,7 @@
           <t>C | 342呎 (1房)
 $895万
 $26,170/呎
-(20年-11月)</t>
+(20年-11月-03日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -8637,7 +8637,7 @@
           <t>D | 527呎 (2房)
 $1599万
 $30,340/呎
-(22年-01月)</t>
+(22年-01月-30日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -8645,7 +8645,7 @@
           <t>E | 332呎 (1房)
 $966万
 $29,087/呎
-(21年-05月)</t>
+(21年-05月-24日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -8653,7 +8653,7 @@
           <t>F | 552呎 (2房)
 $1684万
 $30,498/呎
-(21年-07月)</t>
+(21年-07月-13日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -8661,7 +8661,7 @@
           <t>G | 535呎 (2房)
 $1602万
 $29,936/呎
-(20年-11月)</t>
+(20年-11月-02日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -8669,7 +8669,7 @@
           <t>H | 1257呎 (4+房)
 $3400万
 $27,049/呎
-(22年-10月)</t>
+(22年-10月-31日)</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8684,7 @@
           <t>A | 578呎 (2房)
 $1403万
 $24,266/呎
-(21年-04月)</t>
+(21年-04月-08日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -8692,7 +8692,7 @@
           <t>B | 522呎 (2房)
 $1218万
 $23,343/呎
-(21年-04月)</t>
+(21年-04月-21日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -8700,7 +8700,7 @@
           <t>C | 342呎 (1房)
 $856万
 $25,044/呎
-(20年-11月)</t>
+(20年-11月-03日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -8708,7 +8708,7 @@
           <t>D | 527呎 (2房)
 $1454万
 $27,583/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -8716,7 +8716,7 @@
           <t>E | 332呎 (1房)
 $1028万
 $30,970/呎
-(21年-08月)</t>
+(21年-08月-26日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -8724,7 +8724,7 @@
           <t>F | 552呎 (2房)
 $1581万
 $28,645/呎
-(23年-10月)</t>
+(23年-10月-24日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -8732,7 +8732,7 @@
           <t>G | 535呎 (2房)
 $1661万
 $31,049/呎
-(23年-02月)</t>
+(23年-02月-19日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -8740,7 +8740,7 @@
           <t>H | 1257呎 (4+房)
 $2950万
 $23,469/呎
-(23年-02月)</t>
+(23年-02月-07日)</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8755,7 @@
           <t>A | 556呎 (2房)
 $1268万
 $22,806/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -8763,7 +8763,7 @@
           <t>B | 521呎 (2房)
 $1164万
 $22,338/呎
-(21年-04月)</t>
+(21年-04月-25日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -8771,7 +8771,7 @@
           <t>C | 342呎 (1房)
 $783万
 $22,889/呎
-(20年-11月)</t>
+(20年-11月-01日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -8779,7 +8779,7 @@
           <t>D | 527呎 (2房)
 $1503万
 $28,514/呎
-(22年-07月)</t>
+(22年-07月-06日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -8787,7 +8787,7 @@
           <t>E | 331呎 (1房)
 $910万
 $27,502/呎
-(21年-03月)</t>
+(21年-03月-31日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -8795,7 +8795,7 @@
           <t>F | 552呎 (2房)
 $1587万
 $28,746/呎
-(21年-07月)</t>
+(21年-07月-05日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -8803,7 +8803,7 @@
           <t>G | 534呎 (2房)
 $1442万
 $27,000/呎
-(21年-04月)</t>
+(21年-04月-12日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -8811,7 +8811,7 @@
           <t>H | 1257呎 (4+房)
 $3300万
 $26,253/呎
-(22年-10月)</t>
+(22年-10月-31日)</t>
         </is>
       </c>
     </row>
